--- a/src/main/resources/2012/03/Will_Smith.xlsx
+++ b/src/main/resources/2012/03/Will_Smith.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t xml:space="preserve">Data</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t xml:space="preserve">Dokumentacja techniczna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5</t>
   </si>
   <si>
     <t xml:space="preserve">Nosznie cegieł</t>
@@ -75,10 +78,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="@"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -160,7 +164,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -179,6 +183,14 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -333,7 +345,7 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -344,7 +356,7 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -355,8 +367,8 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>0.5</v>
+      <c r="C4" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -365,9 +377,9 @@
         <v>40973</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -376,9 +388,9 @@
         <v>40974</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="6" t="n">
         <v>8</v>
       </c>
     </row>
@@ -387,9 +399,9 @@
         <v>40975</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -455,9 +467,9 @@
         <v>40969</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="7" t="n">
         <v>4</v>
       </c>
     </row>
@@ -466,9 +478,9 @@
         <v>40970</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3" s="7" t="n">
         <v>7</v>
       </c>
     </row>
@@ -477,7 +489,7 @@
         <v>40971</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>6</v>
@@ -488,7 +500,7 @@
         <v>40975</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>11</v>
@@ -499,7 +511,7 @@
         <v>40976</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>3</v>
@@ -510,7 +522,7 @@
         <v>40978</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>8</v>
@@ -521,7 +533,7 @@
         <v>40986</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>2</v>
